--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1889.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1889.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD3F36A-929D-42AE-AA4B-309E67E91C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E8758F-0DFB-4FC6-AF13-BCAE1453A72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Notes" sheetId="2" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="305">
   <si>
     <t>губ</t>
   </si>
@@ -927,6 +928,27 @@
   </si>
   <si>
     <t>[Астраханская (сумма)]</t>
+  </si>
+  <si>
+    <t>Петербургская губерния без приргородов</t>
+  </si>
+  <si>
+    <t>Губернская сумма чж включает пригороды</t>
+  </si>
+  <si>
+    <t>Ярославская губерния Угличский уезд: 59 973 → 109 973.</t>
+  </si>
+  <si>
+    <t>Тифлисская губерния в Ахалцыхском уезде 49 791 → 58 791.</t>
+  </si>
+  <si>
+    <t>Лифляндская губерния Дерптский уезд: 109 578 → 190 578.</t>
+  </si>
+  <si>
+    <t>Проверкой суммы уездов, величин за соседние годы и величин уездной рождаемости и смертности, устанавливаются опечатки и их исправления</t>
+  </si>
+  <si>
+    <t>Для Ферганской области Наманганский уезд — 192 611 жителей.</t>
   </si>
 </sst>
 </file>
@@ -955,7 +977,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -990,6 +1012,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1003,7 +1031,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1071,6 +1099,9 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1245,6 +1276,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99EF9FDB-F20E-4B9F-A941-0DF180738CAD}">
+  <dimension ref="A3:B15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AP275"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -1252,14 +1328,11 @@
     <col min="1" max="1" width="29.7890625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.62890625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="8.62890625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.47265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.47265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.62890625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.15625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.15625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.62890625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.1015625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.41796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.15625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.62890625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.15625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="2.47265625" customWidth="1"/>
     <col min="14" max="28" width="7.15625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="2.62890625" customWidth="1"/>
@@ -1268,13 +1341,13 @@
     <col min="33" max="33" width="2.5234375" customWidth="1"/>
     <col min="34" max="34" width="8.3671875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="7.68359375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.578125" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="3.68359375" customWidth="1"/>
     <col min="38" max="39" width="4.5234375" bestFit="1" customWidth="1"/>
     <col min="41" max="42" width="5.20703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:42" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1312,23 +1385,23 @@
         <v>280</v>
       </c>
       <c r="M1" s="13"/>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
       <c r="AD1" s="11" t="s">
         <v>281</v>
       </c>
@@ -2123,11 +2196,11 @@
       <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="5">
-        <v>1310891</v>
-      </c>
-      <c r="C15" s="5">
-        <v>65230</v>
+      <c r="B15" s="28">
+        <v>1340891</v>
+      </c>
+      <c r="C15" s="28">
+        <v>56230</v>
       </c>
       <c r="D15" s="5">
         <v>34643</v>
@@ -2207,11 +2280,11 @@
       </c>
       <c r="AH15" s="15">
         <f>AD15-B15</f>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="15">
         <f>AE15-C15</f>
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="15">
         <f>AF15-D15</f>
@@ -2219,19 +2292,19 @@
       </c>
       <c r="AL15" s="17">
         <f>C15/B15*1000</f>
-        <v>49.760048699701194</v>
+        <v>41.934803052597111</v>
       </c>
       <c r="AM15" s="17">
         <f>D15/B15*1000</f>
-        <v>26.427063729936354</v>
+        <v>25.83580619155472</v>
       </c>
       <c r="AO15" s="17">
         <f>AL15-K15</f>
-        <v>0.16004869970119273</v>
+        <v>-7.6651969474028903</v>
       </c>
       <c r="AP15" s="17">
         <f>AM15-L15</f>
-        <v>0.62706372993635284</v>
+        <v>3.5806191554719646E-2</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.55000000000000004">
@@ -6568,8 +6641,8 @@
       <c r="A78" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="5">
-        <v>1218579</v>
+      <c r="B78" s="28">
+        <v>1248579</v>
       </c>
       <c r="C78" s="5">
         <v>37633</v>
@@ -6616,8 +6689,8 @@
       <c r="R78" s="5">
         <v>121219</v>
       </c>
-      <c r="S78" s="5">
-        <v>109578</v>
+      <c r="S78" s="28">
+        <v>190578</v>
       </c>
       <c r="T78" s="5">
         <v>101779</v>
@@ -6636,7 +6709,7 @@
       <c r="AB78" s="5"/>
       <c r="AD78" s="15">
         <f>SUM(N78:AB78)</f>
-        <v>1167579</v>
+        <v>1248579</v>
       </c>
       <c r="AE78" s="15">
         <f>SUM(N79:AB79)</f>
@@ -6648,7 +6721,7 @@
       </c>
       <c r="AH78" s="15">
         <f>AD78-B78</f>
-        <v>-51000</v>
+        <v>0</v>
       </c>
       <c r="AI78" s="15">
         <f>AE78-C78</f>
@@ -6660,19 +6733,19 @@
       </c>
       <c r="AL78" s="17">
         <f>C78/B78*1000</f>
-        <v>30.882692053613265</v>
+        <v>30.14066390672917</v>
       </c>
       <c r="AM78" s="17">
         <f>D78/B78*1000</f>
-        <v>23.500322917102622</v>
+        <v>22.935673273377176</v>
       </c>
       <c r="AO78" s="17">
         <f>AL78-K78</f>
-        <v>0.78269205361326399</v>
+        <v>4.0663906729168531E-2</v>
       </c>
       <c r="AP78" s="17">
         <f>AM78-L78</f>
-        <v>0.60032291710262342</v>
+        <v>3.567327337717785E-2</v>
       </c>
     </row>
     <row r="79" spans="1:42" x14ac:dyDescent="0.55000000000000004">
@@ -7000,7 +7073,7 @@
       <c r="AB84" s="8"/>
       <c r="AD84" s="23">
         <f>SUM(AD75:AD83)</f>
-        <v>2272581</v>
+        <v>2353581</v>
       </c>
       <c r="AE84" s="23">
         <f>SUM(AE75:AE83)</f>
@@ -7012,7 +7085,7 @@
       </c>
       <c r="AH84" s="23">
         <f t="shared" ref="AH84:AJ85" si="2">AD84-B84</f>
-        <v>-61000</v>
+        <v>20000</v>
       </c>
       <c r="AI84" s="23">
         <f t="shared" si="2"/>
@@ -12912,8 +12985,8 @@
       <c r="B165" s="5">
         <v>2827457</v>
       </c>
-      <c r="C165" s="5">
-        <v>149700</v>
+      <c r="C165" s="28">
+        <v>140700</v>
       </c>
       <c r="D165" s="5">
         <v>100954</v>
@@ -12999,7 +13072,7 @@
       </c>
       <c r="AI165" s="15">
         <f>AE165-C165</f>
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="AJ165" s="15">
         <f>AF165-D165</f>
@@ -13007,7 +13080,7 @@
       </c>
       <c r="AL165" s="17">
         <f>C165/B165*1000</f>
-        <v>52.945102259733751</v>
+        <v>49.762029979589435</v>
       </c>
       <c r="AM165" s="17">
         <f>D165/B165*1000</f>
@@ -13015,7 +13088,7 @@
       </c>
       <c r="AO165" s="17">
         <f>AL165-K165</f>
-        <v>3.1451022597337541</v>
+        <v>-3.7970020410561744E-2</v>
       </c>
       <c r="AP165" s="17">
         <f>AM165-L165</f>
@@ -14656,8 +14729,8 @@
       <c r="V188" s="5">
         <v>118105</v>
       </c>
-      <c r="W188" s="5">
-        <v>59973</v>
+      <c r="W188" s="28">
+        <v>109973</v>
       </c>
       <c r="X188" s="5"/>
       <c r="Y188" s="5"/>
@@ -14666,7 +14739,7 @@
       <c r="AB188" s="5"/>
       <c r="AD188" s="15">
         <f>SUM(N188:AB188)</f>
-        <v>1129222</v>
+        <v>1179222</v>
       </c>
       <c r="AE188" s="15">
         <f>SUM(N189:AB189)</f>
@@ -14678,7 +14751,7 @@
       </c>
       <c r="AH188" s="15">
         <f>AD188-B188</f>
-        <v>-63842</v>
+        <v>-13842</v>
       </c>
       <c r="AI188" s="15">
         <f>AE188-C188</f>
@@ -14855,7 +14928,7 @@
       <c r="AB191" s="8"/>
       <c r="AD191" s="23">
         <f>SUM(AD85:AD190)</f>
-        <v>63572668</v>
+        <v>63622668</v>
       </c>
       <c r="AE191" s="23">
         <f>SUM(AE85:AE190)</f>
@@ -14867,7 +14940,7 @@
       </c>
       <c r="AH191" s="23">
         <f t="shared" ref="AH191:AJ192" si="5">AD191-B191</f>
-        <v>-87859</v>
+        <v>-37859</v>
       </c>
       <c r="AI191" s="23">
         <f t="shared" si="5"/>
@@ -15151,7 +15224,7 @@
       <c r="AB195" s="8"/>
       <c r="AD195" s="23">
         <f>AD191+AD84+AD74+AD42+AD192</f>
-        <v>95840567</v>
+        <v>95971567</v>
       </c>
       <c r="AE195" s="23">
         <f>AE191+AE84+AE74+AE42+AE192</f>
@@ -15163,7 +15236,7 @@
       </c>
       <c r="AH195" s="23">
         <f t="shared" ref="AH195:AJ196" si="6">AD195-B195</f>
-        <v>-168859</v>
+        <v>-37859</v>
       </c>
       <c r="AI195" s="23">
         <f t="shared" si="6"/>
@@ -16715,8 +16788,8 @@
       <c r="O218" s="5">
         <v>63799</v>
       </c>
-      <c r="P218" s="5">
-        <v>49791</v>
+      <c r="P218" s="28">
+        <v>58791</v>
       </c>
       <c r="Q218" s="5">
         <v>101482</v>
@@ -16744,7 +16817,7 @@
       <c r="AB218" s="5"/>
       <c r="AD218" s="15">
         <f>SUM(N218:AB218)</f>
-        <v>823384</v>
+        <v>832384</v>
       </c>
       <c r="AE218" s="15">
         <f>C218</f>
@@ -16756,7 +16829,7 @@
       </c>
       <c r="AH218" s="15">
         <f>AD218-B218</f>
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="AI218" s="15">
         <f>AE218-C218</f>
@@ -17126,7 +17199,7 @@
       <c r="AB224" s="8"/>
       <c r="AD224" s="23">
         <f>SUM(AD196:AD223)</f>
-        <v>7703316</v>
+        <v>7712316</v>
       </c>
       <c r="AE224" s="23">
         <f>SUM(AE196:AE223)</f>
@@ -17138,7 +17211,7 @@
       </c>
       <c r="AH224" s="23">
         <f>AD224-B224</f>
-        <v>-20000</v>
+        <v>-11000</v>
       </c>
       <c r="AI224" s="23">
         <f>AE224-C224</f>
@@ -20357,7 +20430,7 @@
       <c r="AB275" s="8"/>
       <c r="AD275" s="23">
         <f>AD274+AD250+AD224+AD195</f>
-        <v>114007750</v>
+        <v>114147750</v>
       </c>
       <c r="AE275" s="23">
         <f>AE274+AE250+AE224+AE195</f>
@@ -20369,7 +20442,7 @@
       </c>
       <c r="AH275" s="23">
         <f t="shared" si="8"/>
-        <v>-368770</v>
+        <v>-228770</v>
       </c>
       <c r="AI275" s="23">
         <f t="shared" si="8"/>
